--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -867,47 +867,47 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -952,52 +952,52 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
@@ -1047,47 +1047,47 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -1137,47 +1137,47 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>13.53</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -1317,47 +1317,47 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -1412,42 +1412,42 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1517,27 +1517,27 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -1587,47 +1587,47 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -1677,22 +1677,22 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
@@ -1702,22 +1702,22 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
     </row>
@@ -1767,47 +1767,47 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -1857,17 +1857,17 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -1877,27 +1877,27 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -1952,42 +1952,42 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -2037,47 +2037,47 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -2127,47 +2127,47 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -2207,57 +2207,57 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -2312,42 +2312,42 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -2397,47 +2397,47 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -2487,47 +2487,47 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -2577,27 +2577,27 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
     </row>
@@ -2667,47 +2667,47 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -2757,17 +2757,17 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -2777,27 +2777,27 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
     </row>
@@ -2937,47 +2937,47 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
     </row>
@@ -3027,47 +3027,47 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -3117,47 +3117,47 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -3212,42 +3212,42 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -3297,47 +3297,47 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -3392,42 +3392,42 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -3487,22 +3487,22 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -3567,47 +3567,47 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -3657,17 +3657,17 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -3677,27 +3677,27 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.7%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
@@ -3772,22 +3772,22 @@
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -3837,22 +3837,22 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
@@ -3862,22 +3862,22 @@
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -3932,42 +3932,42 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -4017,47 +4017,47 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -4112,42 +4112,42 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -4197,47 +4197,47 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -4287,47 +4287,47 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -4377,47 +4377,47 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -4467,47 +4467,47 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -4557,47 +4557,47 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -4647,47 +4647,47 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -4752,32 +4752,32 @@
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -4832,17 +4832,17 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
@@ -4852,22 +4852,22 @@
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
     </row>
@@ -4917,47 +4917,47 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -5007,47 +5007,47 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -5102,42 +5102,42 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
           <t>9.6%</t>
-        </is>
-      </c>
-      <c r="R51" s="7" t="inlineStr">
-        <is>
-          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -5267,57 +5267,57 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -5367,12 +5367,12 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -5382,32 +5382,32 @@
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -5462,17 +5462,17 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
@@ -5482,22 +5482,22 @@
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -5547,22 +5547,22 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
           <t>24.2%</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,32 +5742,32 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -5907,17 +5907,17 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -6087,47 +6087,47 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -6167,57 +6167,57 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
     </row>
@@ -6267,22 +6267,22 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
@@ -6292,22 +6292,22 @@
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>66.4%</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
           <t>13.2%</t>
         </is>
       </c>
-      <c r="P65" s="7" t="inlineStr">
-        <is>
-          <t>68.2%</t>
-        </is>
-      </c>
-      <c r="Q65" s="7" t="inlineStr">
-        <is>
-          <t>11.7%</t>
-        </is>
-      </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -6537,17 +6537,17 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -6567,17 +6567,17 @@
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -6600,14 +6600,14 @@
           <t>G</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>Belgium</t>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -6617,57 +6617,57 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -6690,14 +6690,14 @@
           <t>G</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>Iran</t>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -6707,57 +6707,57 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -6780,14 +6780,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Ghana</t>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>England</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -6797,57 +6797,57 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -6870,14 +6870,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>England</t>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -6887,57 +6887,57 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -6987,22 +6987,22 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
@@ -7012,22 +7012,22 @@
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -7082,42 +7082,42 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -7167,47 +7167,47 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -7257,42 +7257,42 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.7%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.6%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>40.2%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -2517,12 +2517,12 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>25.1%</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="R34" s="7" t="inlineStr">
+        <is>
           <t>6.4%</t>
-        </is>
-      </c>
-      <c r="R34" s="7" t="inlineStr">
-        <is>
-          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3647,12 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5037,17 @@
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -5127,17 +5127,17 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -5217,17 +5217,17 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
@@ -5307,17 +5307,17 @@
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -5667,17 +5667,17 @@
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -5757,17 +5757,17 @@
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.4%</t>
         </is>
       </c>
     </row>
@@ -5847,17 +5847,17 @@
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -6027,17 +6027,17 @@
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -6117,17 +6117,17 @@
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
@@ -6207,17 +6207,17 @@
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -6297,17 +6297,17 @@
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -6387,17 +6387,17 @@
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -6477,17 +6477,17 @@
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -6567,17 +6567,17 @@
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -6657,17 +6657,17 @@
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -6747,17 +6747,17 @@
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -6837,17 +6837,17 @@
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6927,12 @@
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
@@ -7017,17 +7017,17 @@
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.7%</t>
         </is>
       </c>
     </row>
@@ -7107,17 +7107,17 @@
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
     </row>
@@ -7287,17 +7287,17 @@
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
+          <t>11.6%</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
           <t>10.4%</t>
         </is>
       </c>
-      <c r="Q75" s="7" t="inlineStr">
-        <is>
-          <t>11.4%</t>
-        </is>
-      </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F76" s="13" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -8092,12 +8092,12 @@
       <c r="D85" s="11" t="inlineStr"/>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       <c r="D89" s="11" t="inlineStr"/>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       <c r="D92" s="15" t="inlineStr"/>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>71.3%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G97" s="16" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       <c r="D98" s="15" t="inlineStr"/>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -9225,12 +9225,12 @@
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J98" s="15" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.3%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Winner UEFA Playoff D</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -947,57 +947,57 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -1020,14 +1020,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Winner UEFA Playoff A</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1037,57 +1037,57 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -1137,47 +1137,47 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
@@ -1222,52 +1222,52 @@
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
@@ -1312,52 +1312,52 @@
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -1422,32 +1422,32 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -1497,47 +1497,47 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -1592,27 +1592,27 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -1677,47 +1677,47 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -1767,47 +1767,47 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -1847,57 +1847,57 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.3%</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -1952,42 +1952,42 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -2037,22 +2037,22 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.2%</t>
         </is>
       </c>
     </row>
@@ -2127,47 +2127,47 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.9%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -2222,42 +2222,42 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -2327,27 +2327,27 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -2397,17 +2397,17 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
     </row>
@@ -2487,47 +2487,47 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -2582,42 +2582,42 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -2687,27 +2687,27 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -2757,17 +2757,17 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -2847,47 +2847,47 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2952,32 +2952,32 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -3027,47 +3027,47 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -3107,57 +3107,57 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -3207,47 +3207,47 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -3297,47 +3297,47 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
     </row>
@@ -3387,47 +3387,47 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -3477,47 +3477,47 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -3567,32 +3567,32 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -3647,47 +3647,47 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -3737,57 +3737,57 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -3837,42 +3837,42 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
@@ -3932,17 +3932,17 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
@@ -4017,42 +4017,42 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
@@ -4112,42 +4112,42 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -4197,47 +4197,47 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -4287,22 +4287,22 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
@@ -4312,22 +4312,22 @@
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -4467,27 +4467,27 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -4557,32 +4557,32 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -4647,47 +4647,47 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
     </row>
@@ -4737,47 +4737,47 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -4832,42 +4832,42 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -4917,17 +4917,17 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -5007,47 +5007,47 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
     </row>
@@ -5087,47 +5087,47 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -5187,47 +5187,47 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -5267,57 +5267,57 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.6%</t>
         </is>
       </c>
     </row>
@@ -5367,47 +5367,47 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -5457,47 +5457,47 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -5727,37 +5727,37 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
@@ -5917,37 +5917,37 @@
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
@@ -6097,37 +6097,37 @@
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -6177,47 +6177,47 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -6277,37 +6277,37 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -6537,22 +6537,22 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
@@ -6562,22 +6562,22 @@
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
     </row>
@@ -6627,47 +6627,47 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -6717,47 +6717,47 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -6807,47 +6807,47 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -6902,42 +6902,42 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -6987,17 +6987,17 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -7007,27 +7007,27 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -7077,27 +7077,27 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -7167,47 +7167,47 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -7272,32 +7272,32 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -7316,14 +7316,14 @@
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
-      <c r="E76" s="13" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Canada</t>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       <c r="D88" s="11" t="inlineStr"/>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       <c r="D92" s="15" t="inlineStr"/>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J92" s="15" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>42.5%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.5%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       <c r="D99" s="15" t="inlineStr"/>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>74.2%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Winner UEFA Playoff D</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>22.8%</t>
         </is>
       </c>
     </row>
@@ -1020,14 +1020,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Winner UEFA Playoff A</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -1407,47 +1407,47 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -1497,17 +1497,17 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1517,27 +1517,27 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>42.5%</t>
         </is>
       </c>
     </row>
@@ -1592,42 +1592,42 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.3%</t>
         </is>
       </c>
     </row>
@@ -1677,27 +1677,27 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>39.7%</t>
         </is>
       </c>
     </row>
@@ -1767,47 +1767,47 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -1847,57 +1847,57 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -1952,42 +1952,42 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -2037,22 +2037,22 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -2127,47 +2127,47 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -2222,37 +2222,37 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
@@ -2312,42 +2312,42 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
+          <t>21.9%</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>13.4%</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>64.2%</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
           <t>21.8%</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>65.9%</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>12.6%</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
@@ -2422,22 +2422,22 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -2487,47 +2487,47 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -2582,42 +2582,42 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -2667,27 +2667,27 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -2762,22 +2762,22 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="O25" s="7" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -2847,47 +2847,47 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
+          <t>27.9%</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>27.7%</t>
-        </is>
-      </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2952,32 +2952,32 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -3027,47 +3027,47 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -3142,22 +3142,22 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -3207,47 +3207,47 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -3297,47 +3297,47 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -3387,17 +3387,17 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -3407,27 +3407,27 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -3487,27 +3487,27 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -3567,47 +3567,47 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -3657,47 +3657,47 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -3752,42 +3752,42 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -3837,27 +3837,27 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -3932,17 +3932,17 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
@@ -3952,22 +3952,22 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -4017,47 +4017,47 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
     </row>
@@ -4112,42 +4112,42 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -4197,47 +4197,47 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -4292,42 +4292,42 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -4377,47 +4377,47 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
+          <t>25.6%</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
           <t>26.0%</t>
         </is>
       </c>
-      <c r="O43" s="7" t="inlineStr">
-        <is>
-          <t>54.2%</t>
-        </is>
-      </c>
-      <c r="P43" s="7" t="inlineStr">
-        <is>
-          <t>25.5%</t>
-        </is>
-      </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -4472,37 +4472,37 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -4577,27 +4577,27 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -4647,27 +4647,27 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>40.1%</t>
         </is>
       </c>
     </row>
@@ -4737,17 +4737,17 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -4757,27 +4757,27 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -4832,42 +4832,42 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -4922,22 +4922,22 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -5012,42 +5012,42 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -5097,47 +5097,47 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -5277,47 +5277,47 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -5367,17 +5367,17 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -5387,22 +5387,22 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
@@ -5457,47 +5457,47 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -5547,12 +5547,12 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
@@ -5757,17 +5757,17 @@
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -5817,32 +5817,32 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
     </row>
@@ -5907,27 +5907,27 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -5997,47 +5997,47 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -6087,47 +6087,47 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -6177,17 +6177,17 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -6197,27 +6197,27 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -6267,17 +6267,17 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -6287,27 +6287,27 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -6557,27 +6557,27 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -6627,42 +6627,42 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
@@ -6717,47 +6717,47 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>75.4%</t>
         </is>
       </c>
     </row>
@@ -6807,12 +6807,12 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -6827,27 +6827,27 @@
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -6897,42 +6897,42 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
@@ -6987,47 +6987,47 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -7077,47 +7077,47 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -7182,32 +7182,32 @@
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.0%</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -7272,32 +7272,32 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       <c r="D88" s="11" t="inlineStr"/>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       <c r="D92" s="15" t="inlineStr"/>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J92" s="15" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       <c r="D99" s="15" t="inlineStr"/>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.3%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WK 2026 Voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -1407,47 +1407,47 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1497,47 +1497,47 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -1577,57 +1577,57 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>18.60</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -1672,52 +1672,52 @@
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
@@ -1762,52 +1762,52 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -1847,57 +1847,57 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
           <t>H</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -1942,52 +1942,52 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
@@ -2032,52 +2032,52 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
@@ -2122,52 +2122,52 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
@@ -2212,52 +2212,52 @@
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>67.3%</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>12.3%</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
           <t>20.4%</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>69.2%</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -2302,52 +2302,52 @@
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Winner FIFA Playoff 2</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -2387,57 +2387,57 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>87.7%</t>
         </is>
       </c>
     </row>
@@ -2482,52 +2482,52 @@
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -2567,57 +2567,57 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Winner FIFA Playoff 1</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -2657,57 +2657,57 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -2752,52 +2752,52 @@
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
@@ -2842,52 +2842,52 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -2932,52 +2932,52 @@
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -3027,47 +3027,47 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
     </row>
@@ -3107,57 +3107,57 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -3207,47 +3207,47 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -3297,47 +3297,47 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -3387,17 +3387,17 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -3407,27 +3407,27 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -3477,47 +3477,47 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -3572,42 +3572,42 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -3657,47 +3657,47 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -3737,57 +3737,57 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -3837,27 +3837,27 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -3927,47 +3927,47 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -4017,47 +4017,47 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -4107,37 +4107,37 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -4197,47 +4197,47 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.2%</t>
         </is>
       </c>
     </row>
@@ -4287,27 +4287,27 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -4377,47 +4377,47 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
     </row>
@@ -4467,47 +4467,47 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -4557,47 +4557,47 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -4647,47 +4647,47 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -4737,47 +4737,47 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>22.8%</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr">
-        <is>
-          <t>63.1%</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>26.5%</t>
-        </is>
-      </c>
-      <c r="Q47" s="7" t="inlineStr">
-        <is>
-          <t>14.9%</t>
-        </is>
-      </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
     </row>
@@ -4827,47 +4827,47 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -4917,47 +4917,47 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -5007,47 +5007,47 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -5097,47 +5097,47 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -5267,57 +5267,57 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -5367,22 +5367,22 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
@@ -5392,22 +5392,22 @@
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
     </row>
@@ -5457,27 +5457,27 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -5547,47 +5547,47 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -5727,47 +5727,47 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>16.63</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -5907,47 +5907,47 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -5997,47 +5997,47 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -6087,47 +6087,47 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
     </row>
@@ -6182,42 +6182,42 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
     </row>
@@ -6267,17 +6267,17 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -6287,27 +6287,27 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -6537,47 +6537,47 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -6627,47 +6627,47 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -6717,47 +6717,47 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -6807,47 +6807,47 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -6887,57 +6887,57 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -6977,57 +6977,57 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -7077,47 +7077,47 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
           <t>28.4%</t>
         </is>
       </c>
-      <c r="O73" s="7" t="inlineStr">
-        <is>
-          <t>30.8%</t>
-        </is>
-      </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -7167,22 +7167,22 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
@@ -7192,22 +7192,22 @@
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -7257,47 +7257,47 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F76" s="13" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
+          <t>50.2%</t>
+        </is>
+      </c>
+      <c r="Q76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R76" s="11" t="inlineStr">
+        <is>
           <t>49.8%</t>
-        </is>
-      </c>
-      <c r="Q76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R76" s="11" t="inlineStr">
-        <is>
-          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7660,12 @@
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr"/>
-      <c r="E80" s="13" t="inlineStr">
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F80" s="12" t="inlineStr">
+      <c r="F80" s="13" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
@@ -7677,12 +7677,12 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       <c r="D92" s="15" t="inlineStr"/>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J95" s="15" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
     </row>
@@ -9225,12 +9225,12 @@
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J98" s="15" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
         </is>
       </c>
       <c r="D100" s="19" t="inlineStr"/>
-      <c r="E100" s="20" t="inlineStr">
+      <c r="E100" s="21" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F100" s="21" t="inlineStr">
+      <c r="F100" s="20" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
@@ -9397,12 +9397,12 @@
       </c>
       <c r="H100" s="22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I100" s="22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J100" s="19" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="H101" s="22" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I101" s="22" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J101" s="19" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       <c r="D104" s="23" t="inlineStr"/>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F104" s="25" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       <c r="D106" s="27" t="inlineStr"/>
       <c r="E106" s="28" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F106" s="29" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -9999,12 +9999,12 @@
       </c>
       <c r="H107" s="32" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I107" s="32" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J107" s="18" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.4%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.3%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.9%</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>87.2%</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -2937,47 +2937,47 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
@@ -3022,52 +3022,52 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -3112,42 +3112,42 @@
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -3202,52 +3202,52 @@
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>84.2%</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
           <t>9.2%</t>
         </is>
       </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>82.2%</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
-      </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -3297,47 +3297,47 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -3382,52 +3382,52 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -3477,47 +3477,47 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -3562,52 +3562,52 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3630,12 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
@@ -3652,52 +3652,52 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -3737,57 +3737,57 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -3832,52 +3832,52 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
@@ -3922,52 +3922,52 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>6.1%</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>80.7%</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="R38" s="7" t="inlineStr">
+        <is>
           <t>9.1%</t>
-        </is>
-      </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>85.4%</t>
-        </is>
-      </c>
-      <c r="Q38" s="7" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
-      <c r="R38" s="7" t="inlineStr">
-        <is>
-          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -4017,47 +4017,47 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>74.2%</t>
         </is>
       </c>
     </row>
@@ -4107,27 +4107,27 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -4197,27 +4197,27 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -4287,47 +4287,47 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -4387,37 +4387,37 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -4467,47 +4467,47 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -4557,47 +4557,47 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -4647,32 +4647,32 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -4737,22 +4737,22 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
@@ -4762,17 +4762,17 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
@@ -4817,57 +4817,57 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -4917,47 +4917,47 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>87.9%</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
           <t>7.2%</t>
         </is>
       </c>
-      <c r="P49" s="7" t="inlineStr">
-        <is>
-          <t>88.1%</t>
-        </is>
-      </c>
-      <c r="Q49" s="7" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
@@ -5032,22 +5032,22 @@
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -5097,47 +5097,47 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -5187,47 +5187,47 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -5267,57 +5267,57 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -5367,47 +5367,47 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -5457,47 +5457,47 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -5547,47 +5547,47 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -5727,47 +5727,47 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -5817,22 +5817,22 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
@@ -5842,22 +5842,22 @@
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
@@ -5907,47 +5907,47 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -5987,57 +5987,57 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
           <t>10.6%</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="O61" s="7" t="inlineStr">
-        <is>
-          <t>71.3%</t>
-        </is>
-      </c>
-      <c r="P61" s="7" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="Q61" s="7" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -6082,52 +6082,52 @@
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
     </row>
@@ -6177,47 +6177,47 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -6267,47 +6267,47 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -6557,17 +6557,17 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -6627,32 +6627,32 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6707,12 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -6807,47 +6807,47 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -6887,57 +6887,57 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -6987,42 +6987,42 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
@@ -7077,27 +7077,27 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -7277,27 +7277,27 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -7316,14 +7316,14 @@
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
-      <c r="E76" s="13" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Canada</t>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       <c r="D80" s="11" t="inlineStr"/>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F80" s="13" t="inlineStr">
@@ -7677,12 +7677,12 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       <c r="D88" s="11" t="inlineStr"/>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       <c r="D92" s="15" t="inlineStr"/>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J92" s="15" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I94" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J94" s="15" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J95" s="15" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       <c r="D99" s="15" t="inlineStr"/>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="H103" s="22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I103" s="22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J103" s="19" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -3927,37 +3927,37 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -4012,52 +4012,52 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -4102,52 +4102,52 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
@@ -4192,52 +4192,52 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
           <t>H</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
@@ -4282,52 +4282,52 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -4372,52 +4372,52 @@
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>22.9%</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="R43" s="7" t="inlineStr">
+        <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="P43" s="7" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="Q43" s="7" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="R43" s="7" t="inlineStr">
-        <is>
-          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -4462,52 +4462,52 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Winner FIFA Playoff 2</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -4547,57 +4547,57 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>7-0</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>7-0</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -4642,52 +4642,52 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
     </row>
@@ -4732,52 +4732,52 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -4827,47 +4827,47 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -4917,42 +4917,42 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
@@ -5007,47 +5007,47 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -5097,47 +5097,47 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -5187,47 +5187,47 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -5277,47 +5277,47 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
     </row>
@@ -5457,42 +5457,42 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
+          <t>80.9%</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
           <t>80.2%</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>13.8%</t>
-        </is>
-      </c>
-      <c r="O55" s="7" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="P55" s="7" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
@@ -5547,47 +5547,47 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,32 +5742,32 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -5907,47 +5907,47 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -5997,47 +5997,47 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -6087,47 +6087,47 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>36.3%</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
@@ -6172,52 +6172,52 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -6267,47 +6267,47 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -6537,47 +6537,47 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
     </row>
@@ -6627,47 +6627,47 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -6707,57 +6707,57 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -6807,47 +6807,47 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -6897,37 +6897,37 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -6992,42 +6992,42 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -7077,42 +7077,42 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
@@ -7167,47 +7167,47 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -7257,47 +7257,47 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.3%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>42.2%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -8004,14 +8004,14 @@
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
     </row>
@@ -8434,14 +8434,14 @@
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr"/>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Egypt</t>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I94" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J94" s="15" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -9122,12 +9122,12 @@
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr"/>
-      <c r="E97" s="17" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="F97" s="16" t="inlineStr">
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -9139,12 +9139,12 @@
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       <c r="D98" s="15" t="inlineStr"/>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J99" s="15" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>82.3%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="F101" s="20" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G101" s="20" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="H101" s="22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I101" s="22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J101" s="19" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
     </row>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="H103" s="22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I103" s="22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J103" s="19" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="H106" s="30" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I106" s="30" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J106" s="27" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -902,12 +902,12 @@
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.8%</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.4%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.1%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.9%</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.0%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4587,17 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -4647,47 +4647,47 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>32.2%</t>
         </is>
       </c>
     </row>
@@ -4737,47 +4737,47 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -4832,22 +4832,22 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
@@ -4857,17 +4857,17 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -4917,47 +4917,47 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -5007,47 +5007,47 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -5097,47 +5097,47 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -5197,22 +5197,22 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -5277,47 +5277,47 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -5367,47 +5367,47 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -5462,42 +5462,42 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -5547,22 +5547,22 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,32 +5742,32 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -5832,27 +5832,27 @@
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
@@ -5907,42 +5907,42 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -6022,17 +6022,17 @@
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
@@ -6092,22 +6092,22 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
@@ -6117,17 +6117,17 @@
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
     </row>
@@ -6177,47 +6177,47 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -6267,22 +6267,22 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6302,12 +6302,12 @@
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -6362,37 +6362,37 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
@@ -6447,47 +6447,47 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -6537,47 +6537,47 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
     </row>
@@ -6627,47 +6627,47 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -6717,27 +6717,27 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -6807,32 +6807,32 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -6897,47 +6897,47 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -6977,57 +6977,57 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -7082,17 +7082,17 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
@@ -7167,47 +7167,47 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -7257,22 +7257,22 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
@@ -7282,22 +7282,22 @@
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,12 +897,12 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.7%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.9%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4407,12 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -4822,52 +4822,52 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -4912,52 +4912,52 @@
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -5007,47 +5007,47 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -5092,52 +5092,52 @@
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -5187,42 +5187,42 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
@@ -5277,47 +5277,47 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
     </row>
@@ -5367,47 +5367,47 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -5457,47 +5457,47 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
+          <t>80.3%</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
           <t>81.0%</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="O55" s="7" t="inlineStr">
-        <is>
-          <t>5.8%</t>
-        </is>
-      </c>
-      <c r="P55" s="7" t="inlineStr">
-        <is>
-          <t>81.7%</t>
-        </is>
-      </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -5547,47 +5547,47 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,32 +5742,32 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.6%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
@@ -5907,47 +5907,47 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
@@ -6007,22 +6007,22 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.2%</t>
         </is>
       </c>
     </row>
@@ -6177,47 +6177,47 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -6267,47 +6267,47 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -6362,42 +6362,42 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
@@ -6457,37 +6457,37 @@
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -6537,27 +6537,27 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
@@ -6567,17 +6567,17 @@
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -6717,47 +6717,47 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -6807,47 +6807,47 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
+          <t>12.4%</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>80.7%</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>9.3%</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
           <t>13.2%</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
-        <is>
-          <t>78.9%</t>
-        </is>
-      </c>
-      <c r="P70" s="7" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-      <c r="Q70" s="7" t="inlineStr">
-        <is>
-          <t>12.4%</t>
-        </is>
-      </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -6897,47 +6897,47 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -6987,47 +6987,47 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
     </row>
@@ -7072,52 +7072,52 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -7167,47 +7167,47 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -7272,32 +7272,32 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.1%</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.0%</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I102" s="22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
     </row>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="H103" s="22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I103" s="22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J103" s="19" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5007,32 +5007,32 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Winner FIFA Playoff 1</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -5087,57 +5087,57 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -5187,32 +5187,32 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -5367,32 +5367,32 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -5457,32 +5457,32 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -5562,17 +5562,17 @@
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -5832,17 +5832,17 @@
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -5997,32 +5997,32 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6357,32 +6357,32 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
@@ -6447,32 +6447,32 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -6627,32 +6627,32 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -6732,17 +6732,17 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -6807,32 +6807,32 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6897,32 +6897,32 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -7082,27 +7082,27 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
@@ -7257,32 +7257,32 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5007,32 +5007,32 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Winner FIFA Playoff 1</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -5087,57 +5087,57 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -5637,12 +5637,12 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5827,22 +5827,22 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -6987,32 +6987,32 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5007,32 +5007,32 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Winner FIFA Playoff 1</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -5087,57 +5087,57 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -5187,32 +5187,32 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
@@ -5292,17 +5292,17 @@
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -5382,17 +5382,17 @@
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -5647,22 +5647,22 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
@@ -5827,22 +5827,22 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
@@ -6637,22 +6637,22 @@
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>14.38</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -6822,17 +6822,17 @@
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6987,32 +6987,32 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.2%</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Winner FIFA Playoff 2</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -2640,14 +2640,14 @@
           <t>K</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Winner FIFA Playoff 1</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Winner FIFA Playoff 2</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>7-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>7-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -4857,17 +4857,17 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
@@ -5037,17 +5037,17 @@
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Winner FIFA Playoff 1</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -5127,17 +5127,17 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -5182,52 +5182,52 @@
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -5267,57 +5267,57 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -5340,14 +5340,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>Brazil</t>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -5357,57 +5357,57 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -5430,14 +5430,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Haiti</t>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Scotland</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -5447,57 +5447,57 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -5542,52 +5542,52 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -5610,12 +5610,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
@@ -5632,52 +5632,52 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -5727,47 +5727,47 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
@@ -5907,47 +5907,47 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -5997,47 +5997,47 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -6060,14 +6060,14 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -6082,52 +6082,52 @@
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>25.2%</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>Australia</t>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -6172,52 +6172,52 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -6267,47 +6267,47 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -6362,42 +6362,42 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -6447,37 +6447,37 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -6537,47 +6537,47 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
     </row>
@@ -6627,22 +6627,22 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -6732,32 +6732,32 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -6780,14 +6780,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>England</t>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -6797,57 +6797,57 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -6870,14 +6870,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Ghana</t>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>England</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -6887,57 +6887,57 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -6987,47 +6987,47 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
     </row>
@@ -7077,47 +7077,47 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
     </row>
@@ -7167,47 +7167,47 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -7257,37 +7257,37 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.6%</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7318,12 @@
       <c r="D76" s="11" t="inlineStr"/>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="P76" s="11" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Q76" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>78.0%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -8004,14 +8004,14 @@
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="F84" s="13" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -8107,12 +8107,12 @@
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       <c r="D87" s="11" t="inlineStr"/>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
       <c r="D88" s="11" t="inlineStr"/>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       <c r="D91" s="11" t="inlineStr"/>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       <c r="D92" s="15" t="inlineStr"/>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J92" s="15" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G96" s="16" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       <c r="D97" s="15" t="inlineStr"/>
       <c r="E97" s="16" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G98" s="16" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       <c r="D99" s="15" t="inlineStr"/>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J99" s="15" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
         </is>
       </c>
       <c r="D100" s="19" t="inlineStr"/>
-      <c r="E100" s="21" t="inlineStr">
+      <c r="E100" s="20" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F100" s="20" t="inlineStr">
+      <c r="F100" s="21" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
@@ -9397,12 +9397,12 @@
       </c>
       <c r="H100" s="22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I100" s="22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J100" s="19" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I102" s="22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       <c r="D103" s="19" t="inlineStr"/>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
@@ -9655,12 +9655,12 @@
       </c>
       <c r="H103" s="22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I103" s="22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J103" s="19" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       <c r="D104" s="23" t="inlineStr"/>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F104" s="25" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       <c r="D106" s="27" t="inlineStr"/>
       <c r="E106" s="28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F106" s="29" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="H106" s="30" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I106" s="30" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J106" s="27" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,12 +897,12 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.8%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.2%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -4857,17 +4857,17 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -5127,17 +5127,17 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -5367,37 +5367,37 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -5457,47 +5457,47 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -5577,17 +5577,17 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -5667,17 +5667,17 @@
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,32 +5742,32 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -5907,47 +5907,47 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -5997,47 +5997,47 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>28.50</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -6087,37 +6087,37 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
@@ -6192,32 +6192,32 @@
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -6287,17 +6287,17 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -6362,42 +6362,42 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -6447,32 +6447,32 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
@@ -6562,22 +6562,22 @@
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -6657,17 +6657,17 @@
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -6732,32 +6732,32 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -6837,17 +6837,17 @@
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -6927,17 +6927,17 @@
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -6977,22 +6977,22 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -7002,22 +7002,22 @@
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
@@ -7177,37 +7177,37 @@
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -7287,17 +7287,17 @@
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>86.3%</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5367,32 +5367,32 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -5457,32 +5457,32 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -5547,32 +5547,32 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
@@ -5737,22 +5737,22 @@
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -5817,32 +5817,32 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -5907,32 +5907,32 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -5997,32 +5997,32 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
@@ -6187,12 +6187,12 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
@@ -6997,22 +6997,22 @@
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -5547,32 +5547,32 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5727,32 +5727,32 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -5817,32 +5817,32 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -5907,32 +5907,32 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -5997,32 +5997,32 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -6277,22 +6277,22 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6362,27 +6362,27 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
@@ -6447,32 +6447,32 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -6627,32 +6627,32 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -5547,32 +5547,32 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -5817,32 +5817,32 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -5907,32 +5907,32 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -6087,32 +6087,32 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6362,27 +6362,27 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6537,32 +6537,32 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
@@ -6732,17 +6732,17 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -7077,32 +7077,32 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -5547,32 +5547,32 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -5637,32 +5637,32 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
@@ -5817,32 +5817,32 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6627,27 +6627,27 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -4857,17 +4857,17 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5037,17 @@
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -5307,17 +5307,17 @@
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
     </row>
@@ -5397,17 +5397,17 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -5487,17 +5487,17 @@
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -5547,47 +5547,47 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -5637,47 +5637,47 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -5722,52 +5722,52 @@
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5790,12 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -5812,52 +5812,52 @@
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
@@ -5902,52 +5902,52 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -5992,52 +5992,52 @@
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
@@ -6082,52 +6082,52 @@
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6150,12 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -6172,52 +6172,52 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -6267,47 +6267,47 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
     </row>
@@ -6357,27 +6357,27 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -6537,47 +6537,47 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -6627,47 +6627,47 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -6717,47 +6717,47 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
@@ -6832,22 +6832,22 @@
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -6897,47 +6897,47 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -6987,47 +6987,47 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.6%</t>
         </is>
       </c>
     </row>
@@ -7077,47 +7077,47 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -7167,37 +7167,37 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="Q77" s="11" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="Q79" s="11" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="P85" s="11" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="Q85" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R85" s="11" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P87" s="11" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="Q87" s="11" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P92" s="15" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="Q92" s="15" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="R92" s="15" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>69.3%</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I94" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J94" s="15" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
     </row>
@@ -9139,12 +9139,12 @@
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P100" s="19" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="Q100" s="19" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.4%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.8%</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4587,17 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -4857,17 +4857,17 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5037,17 @@
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -5127,17 +5127,17 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -5217,17 +5217,17 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -5307,17 +5307,17 @@
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -5397,17 +5397,17 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -5487,17 +5487,17 @@
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -5577,17 +5577,17 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -5667,17 +5667,17 @@
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -5757,17 +5757,17 @@
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -5847,17 +5847,17 @@
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -5937,17 +5937,17 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -6027,17 +6027,17 @@
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -6117,17 +6117,17 @@
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
     </row>
@@ -6267,47 +6267,47 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -6357,47 +6357,47 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -6447,22 +6447,22 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
@@ -6472,22 +6472,22 @@
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -6537,47 +6537,47 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -6627,47 +6627,47 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
@@ -6742,22 +6742,22 @@
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
@@ -6822,27 +6822,27 @@
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
@@ -6887,57 +6887,57 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -7017,17 +7017,17 @@
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
@@ -7102,22 +7102,22 @@
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
     </row>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -7287,17 +7287,17 @@
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>87.7%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P83" s="11" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="Q83" s="11" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P95" s="15" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="Q95" s="15" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R95" s="15" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="P99" s="15" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="Q99" s="15" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.6%</t>
         </is>
       </c>
     </row>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -1887,17 +1887,17 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3777,17 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -3867,17 +3867,17 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -4857,17 +4857,17 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -5087,14 +5087,14 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -5127,17 +5127,17 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -5217,17 +5217,17 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -5397,17 +5397,17 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -5577,17 +5577,17 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -5667,17 +5667,17 @@
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -5757,17 +5757,17 @@
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -5847,17 +5847,17 @@
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -5937,17 +5937,17 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -6027,17 +6027,17 @@
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -6087,47 +6087,47 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -6177,47 +6177,47 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -6262,52 +6262,52 @@
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>70.9%</t>
         </is>
       </c>
     </row>
@@ -6347,57 +6347,57 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
           <t>Cape Verde</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
@@ -6442,52 +6442,52 @@
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -6537,37 +6537,37 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
@@ -6622,52 +6622,52 @@
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -6712,52 +6712,52 @@
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -6807,47 +6807,47 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -6902,42 +6902,42 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>82.1%</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>8.1%</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
           <t>11.6%</t>
         </is>
       </c>
-      <c r="O71" s="7" t="inlineStr">
-        <is>
-          <t>82.5%</t>
-        </is>
-      </c>
-      <c r="P71" s="7" t="inlineStr">
-        <is>
-          <t>8.1%</t>
-        </is>
-      </c>
-      <c r="Q71" s="7" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.3%</t>
         </is>
       </c>
     </row>
@@ -6982,52 +6982,52 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -7077,47 +7077,47 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
           <t>Algeria</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
@@ -7162,52 +7162,52 @@
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -7257,32 +7257,32 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>87.8%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="Q78" s="11" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="Q80" s="11" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="Q81" s="11" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="P82" s="11" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -8004,14 +8004,14 @@
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Cape Verde</t>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="P84" s="11" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P88" s="11" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
     </row>
@@ -8434,14 +8434,14 @@
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr"/>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F89" s="13" t="inlineStr">
-        <is>
-          <t>Belgium</t>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P89" s="11" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="Q89" s="11" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="P90" s="11" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -8795,12 +8795,12 @@
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J93" s="15" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="P93" s="15" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="R93" s="15" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I94" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J94" s="15" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="15" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Q94" s="15" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="15" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P96" s="15" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="Q96" s="15" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -9122,12 +9122,12 @@
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr"/>
-      <c r="E97" s="16" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F97" s="17" t="inlineStr">
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -9139,12 +9139,12 @@
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="P97" s="15" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="Q97" s="15" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       <c r="D98" s="15" t="inlineStr"/>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="F101" s="20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G101" s="20" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="H101" s="22" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I101" s="22" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J101" s="19" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P101" s="19" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="Q101" s="19" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R101" s="19" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I102" s="22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>33.2%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.3%</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P104" s="23" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="Q104" s="23" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R104" s="23" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="H106" s="30" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I106" s="30" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J106" s="27" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P106" s="27" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Q106" s="27" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R106" s="27" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
     </row>
@@ -9999,12 +9999,12 @@
       </c>
       <c r="H107" s="32" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I107" s="32" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J107" s="18" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P107" s="18" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="Q107" s="18" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -6447,32 +6447,32 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6537,32 +6537,32 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -6627,32 +6627,32 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -6987,32 +6987,32 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="P103" s="19" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q103" s="19" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="R103" s="19" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -6807,32 +6807,32 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -7077,22 +7077,22 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P91" s="11" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="Q91" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="Q105" s="23" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -6267,32 +6267,32 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6357,32 +6357,32 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
@@ -6807,32 +6807,32 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -6987,32 +6987,32 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -7077,32 +7077,32 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -6267,32 +6267,32 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -6357,32 +6357,32 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
@@ -6447,32 +6447,32 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6537,32 +6537,32 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -6627,32 +6627,32 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -6807,32 +6807,32 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -6447,32 +6447,32 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -6537,32 +6537,32 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -6627,32 +6627,32 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P86" s="11" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WK 2026 voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2702,12 +2702,12 @@
       <c r="D81" s="3" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Mexico - Sweden</t>
+          <t>Mexico - Ecuador</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       <c r="D82" s="3" t="inlineStr"/>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>England - Algeria</t>
+          <t>England - DR Congo</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -2750,12 +2750,12 @@
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Belgium - Ecuador</t>
+          <t>Belgium - Senegal</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
       <c r="D87" s="3" t="inlineStr"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Switzerland - Senegal</t>
+          <t>Switzerland - Algeria</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       <c r="D96" s="3" t="inlineStr"/>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Ecuador - United States</t>
+          <t>Belgium - United States</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -3158,7 +3158,7 @@
       <c r="D100" s="3" t="inlineStr"/>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Spain - Ecuador</t>
+          <t>Spain - Belgium</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2635,7 +2635,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2942,12 +2942,12 @@
       <c r="D91" s="3" t="inlineStr"/>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Canada - Germany</t>
+          <t>Canada - Morocco</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       <c r="D99" s="3" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Germany - Brazil</t>
+          <t>Morocco - Brazil</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WK 2026 voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2966,7 +2966,7 @@
       <c r="D92" s="3" t="inlineStr"/>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Brazil - Norway</t>
+          <t>Paraguay - Norway</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -2990,12 +2990,12 @@
       <c r="D93" s="3" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Netherlands - France</t>
+          <t>Brazil - France</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       <c r="D99" s="3" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Morocco - Brazil</t>
+          <t>Morocco - Paraguay</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -3230,7 +3230,7 @@
       <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Brazil - Spain</t>
+          <t>Paraguay - Spain</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -3278,7 +3278,7 @@
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Brazil - France</t>
+          <t>Paraguay - France</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WK 2026 voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WK 2026 voorspellingen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       <c r="D99" s="3" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Morocco - Paraguay</t>
+          <t>Morocco - Norway</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Paraguay - Spain</t>
+          <t>Norway - Spain</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3278,12 @@
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Paraguay - France</t>
+          <t>Norway - France</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2966,12 +2966,12 @@
       <c r="D92" s="3" t="inlineStr"/>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Paraguay - Norway</t>
+          <t>Paraguay - France</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       <c r="D93" s="3" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Brazil - France</t>
+          <t>Brazil - Norway</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       <c r="D99" s="3" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Morocco - Norway</t>
+          <t>Morocco - France</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3182,12 @@
       <c r="D101" s="3" t="inlineStr"/>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>France - England</t>
+          <t>Brazil - England</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Norway - Spain</t>
+          <t>France - Spain</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       <c r="D104" s="3" t="inlineStr"/>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>France - Argentina</t>
+          <t>England - Argentina</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -3278,12 +3278,12 @@
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Norway - France</t>
+          <t>France - England</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3062,12 +3062,12 @@
       <c r="D96" s="3" t="inlineStr"/>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Belgium - United States</t>
+          <t>United States - Belgium</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3038,12 +3038,12 @@
       <c r="D95" s="3" t="inlineStr"/>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Spain - Portugal</t>
+          <t>Portugal - Spain</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3043,7 +3043,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       <c r="D97" s="3" t="inlineStr"/>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Australia - Colombia</t>
+          <t>Argentina - Egypt</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       <c r="D98" s="3" t="inlineStr"/>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Switzerland - Argentina</t>
+          <t>Switzerland - Colombia</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       <c r="D102" s="3" t="inlineStr"/>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Colombia - Argentina</t>
+          <t>Argentina - Colombia</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-0</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3134,12 +3134,12 @@
       <c r="D99" s="3" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Morocco - France</t>
+          <t>France - Morocco</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       <c r="D101" s="3" t="inlineStr"/>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Brazil - England</t>
+          <t>Norway - England</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3163,7 +3163,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3206,12 +3206,12 @@
       <c r="D102" s="3" t="inlineStr"/>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Argentina - Colombia</t>
+          <t>Argentina - Switzerland</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
     </row>

--- a/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
+++ b/github_vercel_app/public/files/Scorito_scores_puur_latest.xlsx
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-2</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
     </row>
